--- a/Table9_BIC_ModeratorSelection.xlsx
+++ b/Table9_BIC_ModeratorSelection.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -26,15 +26,12 @@
     <t xml:space="preserve">SC: Cognitive</t>
   </si>
   <si>
-    <t xml:space="preserve">ERROR</t>
+    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">SC: Structural</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">Outcome: Growth rate</t>
   </si>
   <si>
@@ -53,13 +50,13 @@
     <t xml:space="preserve">Number of SC variables</t>
   </si>
   <si>
+    <t xml:space="preserve">Endogeneity: IV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endogeneity: FE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endogeneity: IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endogeneity: FE</t>
   </si>
   <si>
     <t xml:space="preserve">City-level</t>
@@ -430,7 +427,9 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2"/>
+      <c r="B2" t="n">
+        <v>-6.858</v>
+      </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
@@ -440,189 +439,191 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>-3.111</v>
+        <v>-3.852</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>-4.775</v>
+        <v>-3.097</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>-6.474</v>
+        <v>-5.35</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>-6.861</v>
+        <v>-6.864</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7"/>
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-5.407</v>
+      </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-6.179</v>
+        <v>-5.855</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>1.423</v>
+        <v>-0.113</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>-3.608</v>
+        <v>-2.511</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>1.048</v>
+        <v>1.689</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>-4.785</v>
+        <v>-1.9</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>-5.386</v>
+        <v>-2.934</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>-5.267</v>
+        <v>-4.915</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>-6.809</v>
+        <v>-6.327</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>-6.832</v>
+        <v>-6.842</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>-6.247</v>
+        <v>-5.561</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>-6.846</v>
+        <v>-6.822</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n">
-        <v>-6.48</v>
+        <v>-6.321</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
